--- a/public/exports/55606617.xlsx
+++ b/public/exports/55606617.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports/55606617.xlsx
+++ b/public/exports/55606617.xlsx
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 8</t>
+          <t xml:space="preserve">Sollentuna Alle 4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,20 +1926,20 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J26">
-        <v>537</v>
+        <v>445</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585999</t>
+          <t xml:space="preserve">311586007</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 4</t>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2006,11 +2006,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J27">
-        <v>445</v>
+        <v>1324</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2081,11 +2081,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J28">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2156,11 +2156,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J29">
-        <v>1320</v>
+        <v>493</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2231,11 +2231,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J30">
-        <v>493</v>
+        <v>1324</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2306,11 +2306,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J31">
-        <v>1324</v>
+        <v>1018</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 6</t>
+          <t xml:space="preserve">Høvedstensvej 35</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,20 +2376,20 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2091192</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J32">
-        <v>1018</v>
+        <v>8026</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586007</t>
+          <t xml:space="preserve">311566793</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-08</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 35</t>
+          <t xml:space="preserve">Catherine Boothsvej 22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,30 +2451,30 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091192</t>
+          <t xml:space="preserve">2079383</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J33">
-        <v>8026</v>
+        <v>595</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566793</t>
+          <t xml:space="preserve">311567481</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-08</t>
+          <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catherine Boothsvej 22</t>
+          <t xml:space="preserve">Catherine Boothsvej 24A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2531,11 +2531,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J34">
-        <v>595</v>
+        <v>743</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catherine Boothsvej 24A</t>
+          <t xml:space="preserve">Bødkerporten 1Y</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,30 +2601,30 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079383</t>
+          <t xml:space="preserve">2159266</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J35">
-        <v>743</v>
+        <v>7598</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567481</t>
+          <t xml:space="preserve">311586010</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-13</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkerporten 1Y</t>
+          <t xml:space="preserve">Hvidovrevej 218</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2676,20 +2676,20 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159266</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J36">
-        <v>7598</v>
+        <v>1337</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586010</t>
+          <t xml:space="preserve">311588713</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 218</t>
+          <t xml:space="preserve">Hvidovrevej 440</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J37">
-        <v>1337</v>
+        <v>863</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588713</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2831,11 +2831,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J38">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2906,11 +2906,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J39">
-        <v>861</v>
+        <v>958</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2981,11 +2981,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J40">
-        <v>958</v>
+        <v>858</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 440</t>
+          <t xml:space="preserve">Hvidovrevej 440A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3056,11 +3056,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J41">
-        <v>858</v>
+        <v>6125</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 440A</t>
+          <t xml:space="preserve">Egevolden 106</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,20 +3126,20 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J42">
-        <v>6125</v>
+        <v>4371</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586013</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-01-11</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3206,11 +3206,11 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J43">
-        <v>4371</v>
+        <v>2187</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3281,11 +3281,11 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J44">
-        <v>2187</v>
+        <v>362</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevolden 106</t>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,20 +3351,20 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J45">
-        <v>362</v>
+        <v>894</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586013</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-11</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3431,11 +3431,11 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J46">
-        <v>894</v>
+        <v>568</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3506,11 +3506,11 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J47">
-        <v>568</v>
+        <v>493</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3581,11 +3581,11 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J48">
-        <v>493</v>
+        <v>449</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3656,11 +3656,11 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J49">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J50">
-        <v>445</v>
+        <v>798</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J51">
@@ -3881,11 +3881,11 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J52">
-        <v>798</v>
+        <v>772</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3956,11 +3956,11 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J53">
-        <v>772</v>
+        <v>884</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4031,11 +4031,11 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J54">
-        <v>884</v>
+        <v>621</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J55">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J56">
@@ -4256,11 +4256,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J57">
-        <v>621</v>
+        <v>1214</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+          <t xml:space="preserve">Kettegård Alle 2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,20 +4326,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J58">
-        <v>1214</v>
+        <v>1703</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588729</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 2</t>
+          <t xml:space="preserve">Kettegård Alle 2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,20 +4401,20 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J59">
-        <v>969</v>
+        <v>663</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588722</t>
+          <t xml:space="preserve">311588729</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 4</t>
+          <t xml:space="preserve">Kettegård Alle 2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,20 +4476,20 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J60">
-        <v>5857</v>
+        <v>273</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588721</t>
+          <t xml:space="preserve">311588729</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4556,11 +4556,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J61">
-        <v>1703</v>
+        <v>1925</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 2</t>
+          <t xml:space="preserve">Kettegård Alle 4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J62">
-        <v>663</v>
+        <v>1256</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 2</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,20 +4701,20 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J63">
-        <v>273</v>
+        <v>3240</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311588726</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 2</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,20 +4776,20 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J64">
-        <v>1925</v>
+        <v>554</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311588726</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 4</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,20 +4851,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J65">
-        <v>1256</v>
+        <v>1528</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311588726</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4931,11 +4931,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J66">
-        <v>3240</v>
+        <v>2017</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5006,11 +5006,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J67">
-        <v>554</v>
+        <v>1008</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5081,11 +5081,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J68">
-        <v>1528</v>
+        <v>900</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,20 +5151,20 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J69">
-        <v>2017</v>
+        <v>326</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,20 +5226,20 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J70">
-        <v>1008</v>
+        <v>1167</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J71">
-        <v>900</v>
+        <v>629</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5381,11 +5381,11 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J72">
-        <v>326</v>
+        <v>785</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5456,11 +5456,11 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J73">
-        <v>1167</v>
+        <v>629</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5531,11 +5531,11 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J74">
-        <v>629</v>
+        <v>1151</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5606,11 +5606,11 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J75">
-        <v>785</v>
+        <v>571</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Byvej 78</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,30 +5676,30 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2157348</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>629</v>
+        <v>262</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311590033</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,30 +5751,30 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J77">
-        <v>1151</v>
+        <v>2799</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311590065</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,30 +5826,30 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J78">
-        <v>571</v>
+        <v>1487</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311590063</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 78</t>
+          <t xml:space="preserve">Sollentuna Alle 4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,20 +5901,20 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157348</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J79">
-        <v>262</v>
+        <v>2387</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590033</t>
+          <t xml:space="preserve">311590061</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,20 +5976,20 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J80">
-        <v>2799</v>
+        <v>787</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590065</t>
+          <t xml:space="preserve">311590058</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Trædrejerporten 1A</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,20 +6051,20 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2159280</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J81">
-        <v>1487</v>
+        <v>5757</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590063</t>
+          <t xml:space="preserve">311589965</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 4</t>
+          <t xml:space="preserve">M Bechs Alle 122</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,30 +6126,30 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J82">
-        <v>2387</v>
+        <v>1272</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590061</t>
+          <t xml:space="preserve">311590424</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 6</t>
+          <t xml:space="preserve">M Bechs Alle 122</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,30 +6201,30 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J83">
-        <v>787</v>
+        <v>4563</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590058</t>
+          <t xml:space="preserve">311590424</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trædrejerporten 1A</t>
+          <t xml:space="preserve">M Bechs Alle 122B</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,30 +6276,30 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159280</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J84">
-        <v>5757</v>
+        <v>2141</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589965</t>
+          <t xml:space="preserve">311590424</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,30 +6351,30 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>1272</v>
+        <v>904</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590424</t>
+          <t xml:space="preserve">311598300</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,30 +6426,30 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J86">
-        <v>4563</v>
+        <v>839</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590424</t>
+          <t xml:space="preserve">311601624</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122B</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,30 +6501,30 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J87">
-        <v>2141</v>
+        <v>863</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590424</t>
+          <t xml:space="preserve">311601624</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Egevolden 100</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,20 +6576,20 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J88">
-        <v>904</v>
+        <v>468</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598300</t>
+          <t xml:space="preserve">311601932</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Avedøre Tværvej 135B</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,20 +6651,20 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2159316</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J89">
-        <v>839</v>
+        <v>356</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601624</t>
+          <t xml:space="preserve">311622352</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-19</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Bibliotekvej 62</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2091211</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>863</v>
+        <v>1472</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601624</t>
+          <t xml:space="preserve">311622365</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-19</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevolden 100</t>
+          <t xml:space="preserve">Byvej 78</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">7029060</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="J91">
-        <v>468</v>
+        <v>398</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601932</t>
+          <t xml:space="preserve">311622350</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-20</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avedøre Tværvej 135B</t>
+          <t xml:space="preserve">Bødkerporten 6B</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159316</t>
+          <t xml:space="preserve">2159279</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,11 +6885,11 @@
         </is>
       </c>
       <c r="J92">
-        <v>356</v>
+        <v>1712</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622352</t>
+          <t xml:space="preserve">311622355</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekvej 62</t>
+          <t xml:space="preserve">Egevolden 106</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,20 +6951,20 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091211</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J93">
-        <v>1472</v>
+        <v>3349</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622365</t>
+          <t xml:space="preserve">311622381</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 78</t>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7029060</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J94">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622350</t>
+          <t xml:space="preserve">311622362</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkerporten 6B</t>
+          <t xml:space="preserve">Hvidovrevej 272</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159279</t>
+          <t xml:space="preserve">2091208</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7110,11 +7110,11 @@
         </is>
       </c>
       <c r="J95">
-        <v>1712</v>
+        <v>2623</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622355</t>
+          <t xml:space="preserve">311622363</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevolden 106</t>
+          <t xml:space="preserve">Hvidovrevej 446</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,20 +7176,20 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J96">
-        <v>3349</v>
+        <v>4389</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622381</t>
+          <t xml:space="preserve">311622359</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+          <t xml:space="preserve">Hvidovrevej 241</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7251,20 +7251,20 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">2090160</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J97">
-        <v>402</v>
+        <v>2533</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622362</t>
+          <t xml:space="preserve">311623162</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 272</t>
+          <t xml:space="preserve">Plovheldvej 4A</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7326,30 +7326,30 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091208</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J98">
-        <v>2623</v>
+        <v>1662</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622363</t>
+          <t xml:space="preserve">311641604</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-11-09</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 446</t>
+          <t xml:space="preserve">Plovheldvej 4A</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,30 +7401,30 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J99">
-        <v>4389</v>
+        <v>323</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622359</t>
+          <t xml:space="preserve">311641603</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-11-09</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 241</t>
+          <t xml:space="preserve">Plovheldvej 4A</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,30 +7476,30 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090160</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J100">
-        <v>2533</v>
+        <v>2375</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623162</t>
+          <t xml:space="preserve">311644178</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7556,15 +7556,15 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J101">
-        <v>1662</v>
+        <v>1847</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641604</t>
+          <t xml:space="preserve">311644178</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-09</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7631,15 +7631,15 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J102">
-        <v>323</v>
+        <v>1226</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641603</t>
+          <t xml:space="preserve">311644178</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-09</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7706,11 +7706,11 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J103">
-        <v>2375</v>
+        <v>1301</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7781,11 +7781,11 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J104">
-        <v>1847</v>
+        <v>2569</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -7856,11 +7856,11 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J105">
-        <v>1226</v>
+        <v>606</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plovheldvej 4A</t>
+          <t xml:space="preserve">Hvidovrevej 278</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,30 +7926,30 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>1301</v>
+        <v>1345</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311669671</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plovheldvej 4A</t>
+          <t xml:space="preserve">Hvidovrevej 278</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,30 +8001,30 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J107">
-        <v>2569</v>
+        <v>6142</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311669668</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plovheldvej 4A</t>
+          <t xml:space="preserve">Hvidovrevej 278</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8085,21 +8085,21 @@
         </is>
       </c>
       <c r="J108">
-        <v>606</v>
+        <v>3329</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311669668</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 278</t>
+          <t xml:space="preserve">Hvidovrevej 446</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,20 +8151,20 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J109">
-        <v>1345</v>
+        <v>6161</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669671</t>
+          <t xml:space="preserve">311669688</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 278</t>
+          <t xml:space="preserve">Høvedstensvej 19</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,20 +8226,20 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J110">
-        <v>6142</v>
+        <v>1000</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669668</t>
+          <t xml:space="preserve">311669683</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 278</t>
+          <t xml:space="preserve">Høvedstensvej 19</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,20 +8301,20 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J111">
-        <v>3329</v>
+        <v>580</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669668</t>
+          <t xml:space="preserve">311669684</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 446</t>
+          <t xml:space="preserve">Høvedstensvej 21</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,20 +8376,20 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
-        <v>6161</v>
+        <v>1611</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669688</t>
+          <t xml:space="preserve">311669683</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 19</t>
+          <t xml:space="preserve">Høvedstensvej 21</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8456,15 +8456,15 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J113">
-        <v>1000</v>
+        <v>1223</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669683</t>
+          <t xml:space="preserve">311669685</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 19</t>
+          <t xml:space="preserve">Karise Alle 29</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,20 +8526,20 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">226182</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J114">
-        <v>580</v>
+        <v>1836</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669684</t>
+          <t xml:space="preserve">311669673</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 21</t>
+          <t xml:space="preserve">Karise Alle 31</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">226183</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>1611</v>
+        <v>3484</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669683</t>
+          <t xml:space="preserve">311669673</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 21</t>
+          <t xml:space="preserve">Krogstens Alle 51</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,20 +8676,20 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">226183</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J116">
-        <v>1223</v>
+        <v>3648</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669685</t>
+          <t xml:space="preserve">311669673</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karise Alle 29</t>
+          <t xml:space="preserve">Avedøre Havnevej 37</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">226182</t>
+          <t xml:space="preserve">7706803</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>1836</v>
+        <v>1559</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669673</t>
+          <t xml:space="preserve">311670403</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karise Alle 31</t>
+          <t xml:space="preserve">Bibliotekvej 52A</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">226183</t>
+          <t xml:space="preserve">100191021</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,21 +8835,21 @@
         </is>
       </c>
       <c r="J118">
-        <v>3484</v>
+        <v>569</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669673</t>
+          <t xml:space="preserve">311670402</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogstens Alle 51</t>
+          <t xml:space="preserve">M Bechs Alle 122C</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,20 +8901,20 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">226183</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J119">
-        <v>3648</v>
+        <v>263</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669673</t>
+          <t xml:space="preserve">311670166</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avedøre Havnevej 37</t>
+          <t xml:space="preserve">Tavlekærsvej 164</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7706803</t>
+          <t xml:space="preserve">228813</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,11 +8985,11 @@
         </is>
       </c>
       <c r="J120">
-        <v>1559</v>
+        <v>4660</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670403</t>
+          <t xml:space="preserve">311670401</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekvej 52A</t>
+          <t xml:space="preserve">Tavlekærsvej 166</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">100191021</t>
+          <t xml:space="preserve">228812</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,16 +9060,16 @@
         </is>
       </c>
       <c r="J121">
-        <v>569</v>
+        <v>1671</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670402</t>
+          <t xml:space="preserve">311670400</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122C</t>
+          <t xml:space="preserve">Høvedstensvej 45</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,20 +9126,20 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J122">
-        <v>263</v>
+        <v>1130</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670166</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tavlekærsvej 164</t>
+          <t xml:space="preserve">Høvedstensvej 45</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,20 +9201,20 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">228813</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J123">
-        <v>4660</v>
+        <v>283</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670401</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tavlekærsvej 166</t>
+          <t xml:space="preserve">Høvedstensvej 45B</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">228812</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>1671</v>
+        <v>1050</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670400</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 45</t>
+          <t xml:space="preserve">Høvedstensvej 49</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9356,15 +9356,15 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J125">
-        <v>1130</v>
+        <v>865</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311674026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 45</t>
+          <t xml:space="preserve">Alarmpladsen 3</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,20 +9426,20 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">9494877</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J126">
-        <v>283</v>
+        <v>365</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311707954</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-09-15</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 45B</t>
+          <t xml:space="preserve">Alarmpladsen 6A</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,20 +9501,20 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">8490054</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J127">
-        <v>1050</v>
+        <v>366</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311716208</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 49</t>
+          <t xml:space="preserve">Byvej 248A</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,20 +9576,20 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J128">
-        <v>865</v>
+        <v>619</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674026</t>
+          <t xml:space="preserve">311716210</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarmpladsen 3</t>
+          <t xml:space="preserve">Byvej 248B</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,20 +9651,20 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9494877</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J129">
-        <v>365</v>
+        <v>608</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311707954</t>
+          <t xml:space="preserve">311716211</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-15</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarmpladsen 6A</t>
+          <t xml:space="preserve">Byvej 248C</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,20 +9726,20 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490054</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J130">
-        <v>366</v>
+        <v>619</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716208</t>
+          <t xml:space="preserve">311716212</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 248A</t>
+          <t xml:space="preserve">Byvej 90</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,20 +9801,20 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">2157348</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J131">
-        <v>619</v>
+        <v>680</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716210</t>
+          <t xml:space="preserve">311716215</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 248B</t>
+          <t xml:space="preserve">Byvej 90B</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">2157348</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J132">
-        <v>608</v>
+        <v>284</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716211</t>
+          <t xml:space="preserve">311716216</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 248C</t>
+          <t xml:space="preserve">Bødkerporten 2D</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,20 +9951,20 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">2159279</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J133">
-        <v>619</v>
+        <v>351</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716212</t>
+          <t xml:space="preserve">311716218</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 90</t>
+          <t xml:space="preserve">Bødkerporten 4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,20 +10026,20 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157348</t>
+          <t xml:space="preserve">2159279</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J134">
-        <v>680</v>
+        <v>1201</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716215</t>
+          <t xml:space="preserve">311716217</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 90B</t>
+          <t xml:space="preserve">Fægtesalsvej 11</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,20 +10101,20 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157348</t>
+          <t xml:space="preserve">9889335</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="J135">
-        <v>284</v>
+        <v>687</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716216</t>
+          <t xml:space="preserve">311716220</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkerporten 2D</t>
+          <t xml:space="preserve">Fægtesalsvej 5</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,20 +10176,20 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159279</t>
+          <t xml:space="preserve">9889336</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J136">
-        <v>351</v>
+        <v>1253</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716218</t>
+          <t xml:space="preserve">311716222</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkerporten 4</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159279</t>
+          <t xml:space="preserve">2077515</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J137">
-        <v>1201</v>
+        <v>685</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716217</t>
+          <t xml:space="preserve">311716223</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fægtesalsvej 11</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,20 +10326,20 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889335</t>
+          <t xml:space="preserve">2077515</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J138">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716220</t>
+          <t xml:space="preserve">311716224</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fægtesalsvej 5</t>
+          <t xml:space="preserve">Hvidovrevej 65</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,20 +10401,20 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889336</t>
+          <t xml:space="preserve">2023609</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J139">
-        <v>1253</v>
+        <v>1289</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716222</t>
+          <t xml:space="preserve">311716225</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
+          <t xml:space="preserve">Svendebjergvej 2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077515</t>
+          <t xml:space="preserve">2079445</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10485,11 +10485,11 @@
         </is>
       </c>
       <c r="J140">
-        <v>685</v>
+        <v>616</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716223</t>
+          <t xml:space="preserve">311716226</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
+          <t xml:space="preserve">Vedbyholm 8</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,20 +10551,20 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077515</t>
+          <t xml:space="preserve">2160430</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>685</v>
+        <v>589</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716224</t>
+          <t xml:space="preserve">311716227</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 65</t>
+          <t xml:space="preserve">Vestre Kvartergade 20</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,20 +10626,20 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023609</t>
+          <t xml:space="preserve">9889332</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="J142">
-        <v>1289</v>
+        <v>423</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716225</t>
+          <t xml:space="preserve">311716230</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendebjergvej 2</t>
+          <t xml:space="preserve">Vestre Kvartergade 22</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,20 +10701,20 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079445</t>
+          <t xml:space="preserve">9889334</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="J143">
-        <v>616</v>
+        <v>423</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716226</t>
+          <t xml:space="preserve">311716229</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vedbyholm 8</t>
+          <t xml:space="preserve">Vestre Kvartergade 5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,20 +10776,20 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160430</t>
+          <t xml:space="preserve">9889329</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J144">
-        <v>589</v>
+        <v>335</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716227</t>
+          <t xml:space="preserve">311716228</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Kvartergade 20</t>
+          <t xml:space="preserve">Hovedporten 6</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,20 +10851,20 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889332</t>
+          <t xml:space="preserve">8490055</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J145">
-        <v>423</v>
+        <v>736</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716230</t>
+          <t xml:space="preserve">311723773</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Kvartergade 22</t>
+          <t xml:space="preserve">Idrætsvej 75</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889334</t>
+          <t xml:space="preserve">2079621</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>423</v>
+        <v>916</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716229</t>
+          <t xml:space="preserve">311726046</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Kvartergade 5</t>
+          <t xml:space="preserve">Byvej 56</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,20 +11001,20 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889329</t>
+          <t xml:space="preserve">2157286</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J147">
-        <v>335</v>
+        <v>563</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716228</t>
+          <t xml:space="preserve">311740693</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2034-02-23</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedporten 6</t>
+          <t xml:space="preserve">Bytoften 29</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,20 +11076,20 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490055</t>
+          <t xml:space="preserve">2025808</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>736</v>
+        <v>781</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723773</t>
+          <t xml:space="preserve">311814922</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 75</t>
+          <t xml:space="preserve">Bytoften 29</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,20 +11151,20 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079621</t>
+          <t xml:space="preserve">2025808</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J149">
-        <v>916</v>
+        <v>856</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726046</t>
+          <t xml:space="preserve">311814922</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-30</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 56</t>
+          <t xml:space="preserve">Ejby Alle 34</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157286</t>
+          <t xml:space="preserve">9807242</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>563</v>
+        <v>1483</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740693</t>
+          <t xml:space="preserve">311814923</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-23</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 29</t>
+          <t xml:space="preserve">Gammel Køge Landevej 276</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025808</t>
+          <t xml:space="preserve">7028595</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>781</v>
+        <v>416</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814922</t>
+          <t xml:space="preserve">311814918</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 29</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,20 +11376,20 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025808</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J152">
-        <v>856</v>
+        <v>430</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814922</t>
+          <t xml:space="preserve">311814920</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejby Alle 34</t>
+          <t xml:space="preserve">Hvidovregade 49</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9807242</t>
+          <t xml:space="preserve">8101016</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -11460,11 +11460,11 @@
         </is>
       </c>
       <c r="J153">
-        <v>1483</v>
+        <v>938</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814923</t>
+          <t xml:space="preserve">311814900</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Køge Landevej 276</t>
+          <t xml:space="preserve">Hvidovregade 59</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028595</t>
+          <t xml:space="preserve">2025855</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,11 +11535,11 @@
         </is>
       </c>
       <c r="J154">
-        <v>416</v>
+        <v>361</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814918</t>
+          <t xml:space="preserve">311814917</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Næsborgvej 90</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,20 +11601,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">7028766</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J155">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814920</t>
+          <t xml:space="preserve">311814924</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11661,22 +11661,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">740</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 49</t>
+          <t xml:space="preserve">Svejbækvej 5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">8600</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101016</t>
+          <t xml:space="preserve">1461683</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>938</v>
+        <v>863</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814900</t>
+          <t xml:space="preserve">311814921</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 59</t>
+          <t xml:space="preserve">Østre Messegade 6</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,20 +11751,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025855</t>
+          <t xml:space="preserve">9597370</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">70</t>
         </is>
       </c>
       <c r="J157">
-        <v>361</v>
+        <v>633</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814917</t>
+          <t xml:space="preserve">311814928</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11811,22 +11811,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">706</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næsborgvej 90</t>
+          <t xml:space="preserve">Søren Jeppesens Vej 3</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028766</t>
+          <t xml:space="preserve">4166473</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>458</v>
+        <v>1058</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814924</t>
+          <t xml:space="preserve">311816487</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-03-10</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11886,35 +11886,35 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">740</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svejbækvej 5</t>
+          <t xml:space="preserve">Alarmpladsen 2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8600</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1461683</t>
+          <t xml:space="preserve">9889328</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J159">
-        <v>863</v>
+        <v>925</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814921</t>
+          <t xml:space="preserve">311821763</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Messegade 6</t>
+          <t xml:space="preserve">Femagervej 37</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,20 +11976,20 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9597370</t>
+          <t xml:space="preserve">2024782</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J160">
-        <v>633</v>
+        <v>276</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814928</t>
+          <t xml:space="preserve">311821760</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12036,35 +12036,35 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">706</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søren Jeppesens Vej 3</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 21</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4166473</t>
+          <t xml:space="preserve">2081592</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J161">
-        <v>1058</v>
+        <v>303</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311816487</t>
+          <t xml:space="preserve">311821754</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-10</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarmpladsen 2</t>
+          <t xml:space="preserve">Hvidovrevej 138</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,20 +12126,20 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889328</t>
+          <t xml:space="preserve">2025821</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J162">
-        <v>925</v>
+        <v>384</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821763</t>
+          <t xml:space="preserve">311821758</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Femagervej 37</t>
+          <t xml:space="preserve">Hvidovrevej 280</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,20 +12201,20 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024782</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J163">
-        <v>276</v>
+        <v>6412</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821760</t>
+          <t xml:space="preserve">311821755</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 21</t>
+          <t xml:space="preserve">Hvidovrevej 98</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081592</t>
+          <t xml:space="preserve">2023815</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821754</t>
+          <t xml:space="preserve">311821767</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 138</t>
+          <t xml:space="preserve">Immerkær 38</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025821</t>
+          <t xml:space="preserve">1300623</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>384</v>
+        <v>660</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821758</t>
+          <t xml:space="preserve">311821770</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 280</t>
+          <t xml:space="preserve">Lille Friheden 1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">9590756</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J166">
-        <v>6412</v>
+        <v>498</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821755</t>
+          <t xml:space="preserve">311821766</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 98</t>
+          <t xml:space="preserve">Østre Messegade 5</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,20 +12501,20 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023815</t>
+          <t xml:space="preserve">9889326</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J167">
-        <v>320</v>
+        <v>445</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821767</t>
+          <t xml:space="preserve">311821765</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immerkær 38</t>
+          <t xml:space="preserve">Præstemosen 209</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300623</t>
+          <t xml:space="preserve">2025114</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12585,11 +12585,11 @@
         </is>
       </c>
       <c r="J168">
-        <v>660</v>
+        <v>319</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821770</t>
+          <t xml:space="preserve">311897780</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Friheden 1</t>
+          <t xml:space="preserve">Præstemosen 209</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590756</t>
+          <t xml:space="preserve">2025114</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J169">
-        <v>498</v>
+        <v>1189</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821766</t>
+          <t xml:space="preserve">311897779</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Messegade 5</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 6</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,20 +12726,20 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889326</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J170">
-        <v>445</v>
+        <v>324</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821765</t>
+          <t xml:space="preserve">311903569</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemosen 209</t>
+          <t xml:space="preserve">Strandhavevej 7</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025114</t>
+          <t xml:space="preserve">2081511</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -12810,11 +12810,11 @@
         </is>
       </c>
       <c r="J171">
-        <v>319</v>
+        <v>721</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897780</t>
+          <t xml:space="preserve">311903567</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemosen 209</t>
+          <t xml:space="preserve">Frydenhøjstien 2</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,30 +12876,30 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025114</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
-        <v>1189</v>
+        <v>969</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897779</t>
+          <t xml:space="preserve">311930507</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 6</t>
+          <t xml:space="preserve">Frydenhøjstien 4</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,30 +12951,30 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J173">
-        <v>324</v>
+        <v>5857</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903569</t>
+          <t xml:space="preserve">311930507</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandhavevej 7</t>
+          <t xml:space="preserve">Frydenhøjstien 8</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,30 +13026,30 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081511</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J174">
-        <v>721</v>
+        <v>537</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903567</t>
+          <t xml:space="preserve">311930507</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
